--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B426F96-A680-4D4E-963F-46BEFC0D25B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B007AA-17CD-4D38-A3CE-C377FF348F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1875,113 +1875,223 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>100</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>500</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>600</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B27" s="14">
+        <v>500</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>110</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>450</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B28" s="14">
+        <v>500</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>600</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B29" s="14">
+        <v>600</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>250</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>400</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B007AA-17CD-4D38-A3CE-C377FF348F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B651D15-9DE0-4D0D-9D38-2418EEBD3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2095,25 +2095,47 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>500</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B651D15-9DE0-4D0D-9D38-2418EEBD3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26287CE-7350-4874-A0E4-D6A5FDA919AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2139,47 +2139,91 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>100</v>
+      </c>
+      <c r="E31" s="14">
+        <v>100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>400</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B32" s="14">
+        <v>423</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>100</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>500</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1383</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>57</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26287CE-7350-4874-A0E4-D6A5FDA919AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEA7A26-C6EF-47D2-9B84-DE8CAAE67E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2227,25 +2227,47 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>60</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>600</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEA7A26-C6EF-47D2-9B84-DE8CAAE67E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A15C8B0-F9F4-4AAC-8D14-EBBAD26E6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2271,25 +2271,47 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>620</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A15C8B0-F9F4-4AAC-8D14-EBBAD26E6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3896E1D2-3DDD-48E6-8953-80CB6279ABAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2315,25 +2315,47 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B35" s="14">
+        <v>500</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>500</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3896E1D2-3DDD-48E6-8953-80CB6279ABAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9FA03B-F286-42FE-97F8-30507531E22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2359,25 +2359,47 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B36" s="14">
+        <v>450</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>250</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>500</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9FA03B-F286-42FE-97F8-30507531E22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF290FAD-20DB-4F98-87CC-A148C95441EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2403,47 +2403,91 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>300</v>
+      </c>
+      <c r="G37" s="14">
+        <v>6</v>
+      </c>
+      <c r="H37" s="14">
+        <v>500</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14">
+        <v>400</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF290FAD-20DB-4F98-87CC-A148C95441EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7016671-7924-4711-8D98-2CADA58C12FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2491,25 +2491,47 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>30</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>6</v>
+      </c>
+      <c r="H39" s="14">
+        <v>500</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7016671-7924-4711-8D98-2CADA58C12FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A38D1-31C2-4771-AA37-0A25D2BACFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2535,25 +2535,47 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>100</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>150</v>
+      </c>
+      <c r="G40" s="14">
+        <v>3</v>
+      </c>
+      <c r="H40" s="14">
+        <v>700</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A38D1-31C2-4771-AA37-0A25D2BACFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A5E296-4374-4CCD-8CDC-F42AE189C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2579,25 +2579,47 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>180</v>
+      </c>
+      <c r="E41" s="14">
+        <v>60</v>
+      </c>
+      <c r="F41" s="14">
+        <v>250</v>
+      </c>
+      <c r="G41" s="14">
+        <v>5</v>
+      </c>
+      <c r="H41" s="14">
+        <v>500</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A5E296-4374-4CCD-8CDC-F42AE189C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354ED956-3DF6-4260-BA3A-9AB638AB4BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2623,25 +2623,47 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>60</v>
+      </c>
+      <c r="D42" s="14">
+        <v>200</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>150</v>
+      </c>
+      <c r="G42" s="14">
+        <v>3</v>
+      </c>
+      <c r="H42" s="14">
+        <v>550</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354ED956-3DF6-4260-BA3A-9AB638AB4BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B402D988-160D-49AD-ACBA-0A2372FEEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2667,47 +2667,91 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B43" s="14">
+        <v>500</v>
+      </c>
+      <c r="C43" s="14">
+        <v>60</v>
+      </c>
+      <c r="D43" s="14">
+        <v>400</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>420</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B44" s="14">
+        <v>500</v>
+      </c>
+      <c r="C44" s="14">
+        <v>60</v>
+      </c>
+      <c r="D44" s="14">
+        <v>500</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>350</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B402D988-160D-49AD-ACBA-0A2372FEEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412C7A7B-2CDE-4FE9-A905-48802C194AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2755,25 +2755,47 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B45" s="14">
+        <v>600</v>
+      </c>
+      <c r="C45" s="14">
+        <v>60</v>
+      </c>
+      <c r="D45" s="14">
+        <v>600</v>
+      </c>
+      <c r="E45" s="14">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412C7A7B-2CDE-4FE9-A905-48802C194AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA97D3CA-7283-48A5-9395-9E4CA53A1DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2799,25 +2799,47 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B46" s="14">
+        <v>520</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>500</v>
+      </c>
+      <c r="E46" s="14">
+        <v>100</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>200</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA97D3CA-7283-48A5-9395-9E4CA53A1DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E56241-7F97-4C93-B518-230603B72517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2843,25 +2843,47 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B47" s="14">
+        <v>600</v>
+      </c>
+      <c r="C47" s="14">
+        <v>60</v>
+      </c>
+      <c r="D47" s="14">
+        <v>450</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>270</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E56241-7F97-4C93-B518-230603B72517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDF256A-7E15-4F6D-9499-60A39CF3F964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2887,25 +2887,47 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B48" s="14">
+        <v>420</v>
+      </c>
+      <c r="C48" s="14">
+        <v>60</v>
+      </c>
+      <c r="D48" s="14">
+        <v>500</v>
+      </c>
+      <c r="E48" s="14">
+        <v>60</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>350</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDF256A-7E15-4F6D-9499-60A39CF3F964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA5BAC1-57AC-47B2-98E0-1153B79656FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2931,25 +2931,47 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>600</v>
+      </c>
+      <c r="E49" s="14">
+        <v>150</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>240</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA5BAC1-57AC-47B2-98E0-1153B79656FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD168A6-6FD1-49ED-9FCA-EFFB834C5086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2975,25 +2975,47 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B50" s="14">
+        <v>500</v>
+      </c>
+      <c r="C50" s="14">
+        <v>60</v>
+      </c>
+      <c r="D50" s="14">
+        <v>200</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>680</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD168A6-6FD1-49ED-9FCA-EFFB834C5086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028717EB-E44F-44B3-A9BD-B6D0764E4422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3019,25 +3019,47 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B51" s="14">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14">
+        <v>60</v>
+      </c>
+      <c r="D51" s="14">
+        <v>300</v>
+      </c>
+      <c r="E51" s="14">
+        <v>60</v>
+      </c>
+      <c r="F51" s="14">
+        <v>6</v>
+      </c>
+      <c r="G51" s="14">
+        <v>300</v>
+      </c>
+      <c r="H51" s="14">
+        <v>550</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1396</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>44</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028717EB-E44F-44B3-A9BD-B6D0764E4422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDC8AE6-C138-443B-9ECE-03DC542504EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3063,25 +3063,47 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>50</v>
+      </c>
+      <c r="D52" s="14">
+        <v>300</v>
+      </c>
+      <c r="E52" s="14">
+        <v>100</v>
+      </c>
+      <c r="F52" s="14">
+        <v>6</v>
+      </c>
+      <c r="G52" s="14">
+        <v>300</v>
+      </c>
+      <c r="H52" s="14">
+        <v>550</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1426</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>14</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDC8AE6-C138-443B-9ECE-03DC542504EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87856BDC-972B-4D7A-ADD5-0A74655A367F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3107,25 +3107,47 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B53" s="14">
+        <v>420</v>
+      </c>
+      <c r="C53" s="14">
+        <v>60</v>
+      </c>
+      <c r="D53" s="14">
+        <v>300</v>
+      </c>
+      <c r="E53" s="14">
+        <v>100</v>
+      </c>
+      <c r="F53" s="14">
+        <v>5</v>
+      </c>
+      <c r="G53" s="14">
+        <v>250</v>
+      </c>
+      <c r="H53" s="14">
+        <v>555</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87856BDC-972B-4D7A-ADD5-0A74655A367F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9A3405-BB14-49D8-8FE5-13A58AF131B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3151,25 +3151,47 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B54" s="14">
+        <v>420</v>
+      </c>
+      <c r="C54" s="14">
+        <v>100</v>
+      </c>
+      <c r="D54" s="14">
+        <v>550</v>
+      </c>
+      <c r="E54" s="14">
+        <v>100</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>270</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9A3405-BB14-49D8-8FE5-13A58AF131B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EF03B4-D428-4C33-A26E-52C67C58F4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3195,25 +3195,47 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B55" s="14">
+        <v>420</v>
+      </c>
+      <c r="C55" s="14">
+        <v>100</v>
+      </c>
+      <c r="D55" s="14">
+        <v>550</v>
+      </c>
+      <c r="E55" s="14">
+        <v>100</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>270</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EF03B4-D428-4C33-A26E-52C67C58F4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE44D080-D492-4C1A-9D90-78C2F1E2BDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3239,25 +3239,47 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B56" s="14">
+        <v>420</v>
+      </c>
+      <c r="C56" s="14">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14">
+        <v>700</v>
+      </c>
+      <c r="E56" s="14">
+        <v>100</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>160</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE44D080-D492-4C1A-9D90-78C2F1E2BDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF7DA55-767C-4145-9F4F-EFA7C4B6819C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3283,25 +3283,47 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>600</v>
+      </c>
+      <c r="E57" s="14">
+        <v>60</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>330</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF7DA55-767C-4145-9F4F-EFA7C4B6819C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AF3CA0-BF85-4388-87EB-E38F35D6B9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3327,25 +3327,47 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>700</v>
+      </c>
+      <c r="E58" s="14">
+        <v>100</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>190</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AF3CA0-BF85-4388-87EB-E38F35D6B9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F241A579-CEF1-4EE6-9B18-C16224D50288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3371,25 +3371,47 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B59" s="14">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14">
+        <v>600</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>360</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F241A579-CEF1-4EE6-9B18-C16224D50288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6719DF-F3F1-4D31-B6C2-CAA8BAE745EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3415,25 +3415,47 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>60</v>
+      </c>
+      <c r="D60" s="14">
+        <v>600</v>
+      </c>
+      <c r="E60" s="14">
+        <v>30</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>300</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>30</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6719DF-F3F1-4D31-B6C2-CAA8BAE745EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECA8D6F-A640-41EF-B6D0-4BF217E7E205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3459,25 +3459,47 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B61" s="14">
+        <v>360</v>
+      </c>
+      <c r="C61" s="14">
+        <v>60</v>
+      </c>
+      <c r="D61" s="14">
+        <v>700</v>
+      </c>
+      <c r="E61" s="14">
+        <v>30</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>290</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECA8D6F-A640-41EF-B6D0-4BF217E7E205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C627245-415E-467A-A06E-AADA8BC3133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3503,25 +3503,47 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B62" s="14">
+        <v>360</v>
+      </c>
+      <c r="C62" s="14">
+        <v>30</v>
+      </c>
+      <c r="D62" s="14">
+        <v>750</v>
+      </c>
+      <c r="E62" s="14">
+        <v>30</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>270</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C627245-415E-467A-A06E-AADA8BC3133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C3C717-A338-420F-88C2-E38471D4A04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3547,25 +3547,47 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B63" s="14">
+        <v>400</v>
+      </c>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>700</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>280</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C3C717-A338-420F-88C2-E38471D4A04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF7F548-023C-457A-8A49-F6F1E5485F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3591,25 +3591,47 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B64" s="14">
+        <v>300</v>
+      </c>
+      <c r="C64" s="14">
+        <v>30</v>
+      </c>
+      <c r="D64" s="14">
+        <v>700</v>
+      </c>
+      <c r="E64" s="14">
+        <v>100</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>250</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF7F548-023C-457A-8A49-F6F1E5485F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C73619-D4C4-4A62-8BF3-C775989878E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3635,25 +3635,47 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B65" s="14">
+        <v>500</v>
+      </c>
+      <c r="C65" s="14">
+        <v>60</v>
+      </c>
+      <c r="D65" s="14">
+        <v>500</v>
+      </c>
+      <c r="E65" s="14">
+        <v>100</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>260</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+        <v>20</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C73619-D4C4-4A62-8BF3-C775989878E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B5049C-71D3-4584-ADED-396EBEDADCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="384" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3679,25 +3679,47 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B66" s="14">
+        <v>500</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>450</v>
+      </c>
+      <c r="E66" s="14">
+        <v>150</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>310</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B5049C-71D3-4584-ADED-396EBEDADCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB238A50-08B3-4CA2-A5D4-721E16758CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="384" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3723,25 +3723,47 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>30</v>
+      </c>
+      <c r="D67" s="14">
+        <v>250</v>
+      </c>
+      <c r="E67" s="14">
+        <v>60</v>
+      </c>
+      <c r="F67" s="14">
+        <v>300</v>
+      </c>
+      <c r="G67" s="14">
+        <v>6</v>
+      </c>
+      <c r="H67" s="14">
+        <v>380</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB238A50-08B3-4CA2-A5D4-721E16758CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FBC186-8874-4495-80EB-6D256A25CD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3767,25 +3767,47 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B68" s="14">
+        <v>420</v>
+      </c>
+      <c r="C68" s="14">
+        <v>30</v>
+      </c>
+      <c r="D68" s="14">
+        <v>300</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>200</v>
+      </c>
+      <c r="G68" s="14">
+        <v>4</v>
+      </c>
+      <c r="H68" s="14">
+        <v>400</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FBC186-8874-4495-80EB-6D256A25CD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E79CAB-05C0-4463-AB9B-AC982B1B39B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3811,25 +3811,47 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B69" s="14">
+        <v>520</v>
+      </c>
+      <c r="C69" s="14">
+        <v>60</v>
+      </c>
+      <c r="D69" s="14">
+        <v>200</v>
+      </c>
+      <c r="E69" s="14">
+        <v>100</v>
+      </c>
+      <c r="F69" s="14">
+        <v>300</v>
+      </c>
+      <c r="G69" s="14">
+        <v>6</v>
+      </c>
+      <c r="H69" s="14">
+        <v>60</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E79CAB-05C0-4463-AB9B-AC982B1B39B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03988E79-1DDB-477E-8440-A67BC661C093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3855,25 +3855,47 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B70" s="14">
+        <v>420</v>
+      </c>
+      <c r="C70" s="14">
+        <v>60</v>
+      </c>
+      <c r="D70" s="14">
+        <v>500</v>
+      </c>
+      <c r="E70" s="14">
+        <v>60</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>400</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03988E79-1DDB-477E-8440-A67BC661C093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479660F1-999F-4794-ABD7-2F03390EECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3899,25 +3899,47 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B71" s="14">
+        <v>420</v>
+      </c>
+      <c r="C71" s="14">
+        <v>30</v>
+      </c>
+      <c r="D71" s="14">
+        <v>300</v>
+      </c>
+      <c r="E71" s="14">
+        <v>200</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>400</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479660F1-999F-4794-ABD7-2F03390EECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E024B0-987A-4E6B-8174-15CDEBABC6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3943,25 +3943,47 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>0</v>
+      </c>
+      <c r="D72" s="14">
+        <v>250</v>
+      </c>
+      <c r="E72" s="14">
+        <v>250</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>520</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E024B0-987A-4E6B-8174-15CDEBABC6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CC43FF-0A62-4492-B551-B93A727876E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3987,25 +3987,47 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B73" s="14">
+        <v>520</v>
+      </c>
+      <c r="C73" s="14">
+        <v>0</v>
+      </c>
+      <c r="D73" s="14">
+        <v>0</v>
+      </c>
+      <c r="E73" s="14">
+        <v>0</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>920</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CC43FF-0A62-4492-B551-B93A727876E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792D060-BEA9-45B7-9192-A84F8BC65FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4031,47 +4031,91 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B74" s="14">
+        <v>420</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>200</v>
+      </c>
+      <c r="E74" s="14">
+        <v>50</v>
+      </c>
+      <c r="F74" s="14">
+        <v>300</v>
+      </c>
+      <c r="G74" s="14">
+        <v>6</v>
+      </c>
+      <c r="H74" s="14">
+        <v>440</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B75" s="14">
+        <v>420</v>
+      </c>
+      <c r="C75" s="14">
+        <v>60</v>
+      </c>
+      <c r="D75" s="14">
+        <v>300</v>
+      </c>
+      <c r="E75" s="14">
+        <v>60</v>
+      </c>
+      <c r="F75" s="14">
+        <v>200</v>
+      </c>
+      <c r="G75" s="14">
+        <v>4</v>
+      </c>
+      <c r="H75" s="14">
+        <v>400</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
